--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.93935953712482</v>
+        <v>13.96514592478278</v>
       </c>
       <c r="D2" t="n">
-        <v>85.48207060883294</v>
+        <v>13.89083647393535</v>
       </c>
       <c r="E2" t="n">
-        <v>26.30456541659916</v>
+        <v>4.274491880197364</v>
       </c>
       <c r="F2" t="n">
-        <v>26.2260201198486</v>
+        <v>4.261728269475397</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>89.82357018054837</v>
+        <v>14.59633015433911</v>
       </c>
       <c r="D3" t="n">
-        <v>89.22426004199575</v>
+        <v>14.49894225682431</v>
       </c>
       <c r="E3" t="n">
-        <v>26.30456541659916</v>
+        <v>4.274491880197364</v>
       </c>
       <c r="F3" t="n">
-        <v>26.2260201198486</v>
+        <v>4.261728269475397</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>105.5244486001907</v>
+        <v>17.14772289753098</v>
       </c>
       <c r="D4" t="n">
-        <v>105.3893090851713</v>
+        <v>17.12576272634034</v>
       </c>
       <c r="E4" t="n">
-        <v>26.30456541659916</v>
+        <v>4.274491880197364</v>
       </c>
       <c r="F4" t="n">
-        <v>26.2260201198486</v>
+        <v>4.261728269475397</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>88.21284396727643</v>
+        <v>14.33458714468242</v>
       </c>
       <c r="D5" t="n">
-        <v>87.96973576200641</v>
+        <v>14.29508206132604</v>
       </c>
       <c r="E5" t="n">
-        <v>26.30456541659916</v>
+        <v>4.274491880197364</v>
       </c>
       <c r="F5" t="n">
-        <v>26.2260201198486</v>
+        <v>4.261728269475397</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>65.54777246936945</v>
+        <v>10.65151302627254</v>
       </c>
       <c r="D6" t="n">
-        <v>65.06159601376471</v>
+        <v>10.57250935223677</v>
       </c>
       <c r="E6" t="n">
-        <v>26.30456541659916</v>
+        <v>4.274491880197364</v>
       </c>
       <c r="F6" t="n">
-        <v>26.2260201198486</v>
+        <v>4.261728269475397</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.72301580384763</v>
+        <v>3.85499006812524</v>
       </c>
       <c r="D7" t="n">
-        <v>23.69806147607182</v>
+        <v>3.85093498986167</v>
       </c>
       <c r="E7" t="n">
-        <v>26.30456541659916</v>
+        <v>4.274491880197364</v>
       </c>
       <c r="F7" t="n">
-        <v>26.2260201198486</v>
+        <v>4.261728269475397</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
